--- a/tables/Table_2_signature_summary.xlsx
+++ b/tables/Table_2_signature_summary.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="Rc3a6005c9e964c09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="Rec6c57ec63be4ec7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R3a090672b4594873"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" r:id="R830c95d988224692"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -544,7 +544,7 @@
         <x:v>Manuscript</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
-        <x:v>Scientific_Reports_Manuscript.docx</x:v>
+        <x:v>Legacy manuscript source (journal-specific filename normalized in v1.3.1)</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
